--- a/Creation_CapabilityStatements/ig/all-profiles.xlsx
+++ b/Creation_CapabilityStatements/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-20T08:08:33+00:00</t>
+    <t>2024-06-20T09:02:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
